--- a/issue-report-extension/templates/comments-template.xlsx
+++ b/issue-report-extension/templates/comments-template.xlsx
@@ -20,18 +20,18 @@
     <font>
       <sz val="10"/>
       <color indexed="8"/>
-      <name val="Helvetica Neue"/>
+      <name val="현대산스 Text Medium"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color indexed="8"/>
-      <name val="Helvetica Neue"/>
+      <name val="현대산스 Text Medium"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="나눔명조"/>
+      <name val="현대산스 Text Medium"/>
       <family val="3"/>
       <charset val="129"/>
     </font>
@@ -39,27 +39,27 @@
       <b/>
       <sz val="16"/>
       <color indexed="8"/>
-      <name val="Helvetica Neue"/>
+      <name val="현대산스 Text Medium"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
-      <name val="Batang"/>
+      <name val="현대산스 Text Medium"/>
       <family val="2"/>
       <charset val="129"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
-      <name val="Batang"/>
+      <name val="현대산스 Text Medium"/>
       <family val="1"/>
       <charset val="129"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
-      <name val="Helvetica Neue"/>
+      <name val="현대산스 Text Medium"/>
       <family val="2"/>
     </font>
   </fonts>
